--- a/public/default-plan.xlsx
+++ b/public/default-plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalimahshowkat/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalimahshowkat/Downloads/capacity engine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD493B95-92BA-0845-8420-BCCBE49BA4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905C617E-5C6D-9646-A362-F4EAF90BBFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17100" activeTab="1" xr2:uid="{7E25AF56-9510-7045-9697-BD4C5339714E}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer 360'!$A$1:$AI$233</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Demand Base Matrix'!$A$1:$J$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Project List'!$A$1:$CS$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Project List'!$A$1:$AM$109</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="829">
   <si>
     <t>Summary</t>
   </si>
@@ -2544,9 +2544,6 @@
   </si>
   <si>
     <t>Julia  Hussey</t>
-  </si>
-  <si>
-    <t>Shravani  Eleswarapu</t>
   </si>
   <si>
     <t>Jackson Purchase Energy</t>
@@ -12664,7 +12661,7 @@
     </row>
     <row r="27" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B27" t="s">
         <v>59</v>
@@ -12848,7 +12845,7 @@
     </row>
     <row r="28" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B28" t="s">
         <v>59</v>
@@ -23893,7 +23890,7 @@
         <v>69</v>
       </c>
       <c r="E95" t="s">
-        <v>826</v>
+        <v>699</v>
       </c>
       <c r="F95" t="s">
         <v>185</v>
@@ -24018,7 +24015,7 @@
         <v>811</v>
       </c>
       <c r="B96" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
@@ -25887,6 +25884,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM109" xr:uid="{AA519189-71C6-1A4D-8254-084482F66B2C}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:AB109" xr:uid="{14286DCC-D056-4C44-B9F7-49C5FE842B7A}">
@@ -48853,6 +48851,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <path xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </path>
+    <LastModified xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="71e11cde-6f33-435a-aab3-afa36e73984d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A57209772119C64B8322F6F07A439EA6" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94fb0221fb477db87fc9f192e3eda52d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed9f1829-d5ed-46f4-83ed-e925f2467574" xmlns:ns3="71e11cde-6f33-435a-aab3-afa36e73984d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6fe001f2bed4f7ac0f88e8497c55b904" ns2:_="" ns3:_="">
     <xsd:import namespace="ed9f1829-d5ed-46f4-83ed-e925f2467574"/>
@@ -49132,46 +49155,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <path xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </path>
-    <LastModified xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed9f1829-d5ed-46f4-83ed-e925f2467574">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="71e11cde-6f33-435a-aab3-afa36e73984d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2104F7F0-8429-4DAF-9F13-08E502323C77}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF139C5-1786-4332-A185-7214EACD463C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ed9f1829-d5ed-46f4-83ed-e925f2467574"/>
-    <ds:schemaRef ds:uri="71e11cde-6f33-435a-aab3-afa36e73984d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -49194,9 +49181,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF139C5-1786-4332-A185-7214EACD463C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2104F7F0-8429-4DAF-9F13-08E502323C77}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ed9f1829-d5ed-46f4-83ed-e925f2467574"/>
+    <ds:schemaRef ds:uri="71e11cde-6f33-435a-aab3-afa36e73984d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
